--- a/09_02.xlsx
+++ b/09_02.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuLieuCua_Sang\HK261\Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuLieuCua_Sang\HK261\Testing\Project\09_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633AFC41-8C34-4F26-8F3B-0B732E20AB42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D419A33-AE3A-42D3-B467-105CDC836924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{24A087C9-FC7B-41A3-BD57-B9096DC3F569}"/>
   </bookViews>
   <sheets>
     <sheet name="0. Cover Page" sheetId="1" r:id="rId1"/>
     <sheet name="1. White Box" sheetId="2" r:id="rId2"/>
+    <sheet name="2. JUnit Test Result" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>ĐỒ ÁN CUỐI KÌ</t>
   </si>
@@ -70,9 +71,6 @@
     <t>khanh.2474801030029@vanlanguni.vn</t>
   </si>
   <si>
-    <t>TÍNH GIÁ VÉ MÁY BAY</t>
-  </si>
-  <si>
     <t>Testcase ID</t>
   </si>
   <si>
@@ -95,6 +93,21 @@
   </si>
   <si>
     <t xml:space="preserve">Bảng quyết định só 1 </t>
+  </si>
+  <si>
+    <t>Đề 2: TÍNH GIÁ VÉ MÁY BAY</t>
+  </si>
+  <si>
+    <t>TC_01: giải thích cột nào của bảng quyết định</t>
+  </si>
+  <si>
+    <t>20% test case fail</t>
+  </si>
+  <si>
+    <t>Chuoj hình kết quả các testcases Failed</t>
+  </si>
+  <si>
+    <t>Xuất toàn bộ kết quả ra file JUnitTestResult.csv</t>
   </si>
 </sst>
 </file>
@@ -184,6 +197,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>120650</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>141</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE935882-067B-13CD-6517-9CD6146D96A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7156450" y="95250"/>
+          <a:ext cx="8286750" cy="25869900"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -568,7 +636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7F2656-C2F3-45D0-B2D5-24D480F4A636}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:Y10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.54296875" customWidth="1"/>
@@ -577,70 +645,98 @@
     <col min="4" max="4" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
     </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D49E8C-3D16-4DF4-BEED-63520DF02D1C}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/09_02.xlsx
+++ b/09_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuLieuCua_Sang\HK261\Testing\Project\09_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D419A33-AE3A-42D3-B467-105CDC836924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3858C1D5-D35D-4471-AE48-63002F3A58B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{24A087C9-FC7B-41A3-BD57-B9096DC3F569}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="272">
   <si>
     <t>ĐỒ ÁN CUỐI KÌ</t>
   </si>
@@ -86,35 +86,770 @@
     <t>Notes</t>
   </si>
   <si>
-    <t>TC02_Condition</t>
-  </si>
-  <si>
     <t>TC01_Path</t>
   </si>
   <si>
-    <t xml:space="preserve">Bảng quyết định só 1 </t>
-  </si>
-  <si>
     <t>Đề 2: TÍNH GIÁ VÉ MÁY BAY</t>
   </si>
   <si>
-    <t>TC_01: giải thích cột nào của bảng quyết định</t>
-  </si>
-  <si>
-    <t>20% test case fail</t>
-  </si>
-  <si>
     <t>Chuoj hình kết quả các testcases Failed</t>
   </si>
   <si>
     <t>Xuất toàn bộ kết quả ra file JUnitTestResult.csv</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Business", soNgayDatTruoc = -4, thuBay = 4, hanhLy = 5, thanhVien = "Silver", ngayLe = true, giaVeCoBan = 1200000</t>
+  </si>
+  <si>
+    <t>Du lieu khong hop le</t>
+  </si>
+  <si>
+    <t>TC02_Path</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 2, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>TC03_Path</t>
+  </si>
+  <si>
+    <t>TC04_Path</t>
+  </si>
+  <si>
+    <t>TC05_Path</t>
+  </si>
+  <si>
+    <t>TC06_Path</t>
+  </si>
+  <si>
+    <t>TC07_Path</t>
+  </si>
+  <si>
+    <t>TC08_Path</t>
+  </si>
+  <si>
+    <t>TC09_Path</t>
+  </si>
+  <si>
+    <t>TC10_Path</t>
+  </si>
+  <si>
+    <t>TC11_Path</t>
+  </si>
+  <si>
+    <t>TC12_Path</t>
+  </si>
+  <si>
+    <t>TC13_Path</t>
+  </si>
+  <si>
+    <t>TC14_Path</t>
+  </si>
+  <si>
+    <t>loaiVe = "KhuHoi", hangGhe = "Economy", soNgayDatTruoc = 2, thuBay = 6, hanhLy = 16, thanhVien = "Silver", ngayLe = false, giaVeCoBan = 1100000</t>
+  </si>
+  <si>
+    <t>loaiVe == null</t>
+  </si>
+  <si>
+    <t>hangGhe == null</t>
+  </si>
+  <si>
+    <t>thanhVien == null</t>
+  </si>
+  <si>
+    <t>!loaiVe.equals("MotChieu")</t>
+  </si>
+  <si>
+    <t>!loaiVe.equals("KhuHoi")</t>
+  </si>
+  <si>
+    <t>!hangGhe.equals("Economy")</t>
+  </si>
+  <si>
+    <t>!hangGhe.equals("Business")</t>
+  </si>
+  <si>
+    <t>!hangGhe.equals("FirstClass")</t>
+  </si>
+  <si>
+    <t>!thanhVien.equals("Thuong")</t>
+  </si>
+  <si>
+    <t>!thanhVien.equals("Silver")</t>
+  </si>
+  <si>
+    <t>!thanhVien.equals("Gold")</t>
+  </si>
+  <si>
+    <t>!thanhVien.equals("Platinum")</t>
+  </si>
+  <si>
+    <t>soNgayDatTruoc &lt; 0</t>
+  </si>
+  <si>
+    <t>thuBay &lt; 1</t>
+  </si>
+  <si>
+    <t>thuBay &gt; 7</t>
+  </si>
+  <si>
+    <t>!Double.isFinite(hanhLy)</t>
+  </si>
+  <si>
+    <t>hanhLy &lt; 0</t>
+  </si>
+  <si>
+    <t>hanhLy &gt; 30</t>
+  </si>
+  <si>
+    <t>!Double.isFinite(giaVeCoBan)</t>
+  </si>
+  <si>
+    <t>giaVeCoBan &lt;= 0</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>loaiVe == null || ( !loaiVe.equals("MotChieu") &amp;&amp; !loaiVe.equals("KhuHoi"))</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>hangGhe == null || (!hangGhe.equals("Economy") &amp;&amp; !hangGhe.equals("Business") &amp;&amp; !hangGhe.equals("FirstClass"))</t>
+  </si>
+  <si>
+    <t>thanhVien == null || (!thanhVien.equals("Thuong") &amp;&amp; !thanhVien.equals("Silver") &amp;&amp; !thanhVien.equals("Gold") &amp;&amp; !thanhVien.equals("Platinum"))</t>
+  </si>
+  <si>
+    <t>soNgayDatTruoc &lt; 0 || thuBay &lt; 1 || thuBay &gt; 7 || !Double.isFinite(hanhLy) || hanhLy &lt; 0 || hanhLy &gt; 30 || !Double.isFinite(giaVeCoBan) || giaVeCoBan &lt;= 0</t>
+  </si>
+  <si>
+    <t>ngayLe &amp;&amp; (thuBay == 5 || thuBay == 6 || thuBay == 7)</t>
+  </si>
+  <si>
+    <t>ngayLe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thuBay == 5 </t>
+  </si>
+  <si>
+    <t>thuBay == 6</t>
+  </si>
+  <si>
+    <t>thuBay == 7</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 1</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 2</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 5</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 6</t>
+  </si>
+  <si>
+    <t>thuBay == 5 || thuBay == 6 || thuBay == 7</t>
+  </si>
+  <si>
+    <t>thuBay == 5</t>
+  </si>
+  <si>
+    <t>hanhLy &gt; 7 &amp;&amp; (thanhVien.equals("Gold") || thanhVien.equals("Platinum"))</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 7</t>
+  </si>
+  <si>
+    <t>hanhLy &gt; 7</t>
+  </si>
+  <si>
+    <t>thanhVien.equals("Gold")</t>
+  </si>
+  <si>
+    <t>thanhVien.equals("Platinum")</t>
+  </si>
+  <si>
+    <t>hanhLy &gt; 7 &amp;&amp; thanhVien.equals("Silver")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hanhLy &gt; 7 </t>
+  </si>
+  <si>
+    <t>thanhVien.equals("Silver")</t>
+  </si>
+  <si>
+    <t>Bảng quyết định số 8</t>
+  </si>
+  <si>
+    <t>Kiểm tra số ngày đặt trước âm</t>
+  </si>
+  <si>
+    <t>Nhánh kiểm tra dữ liệu không hợp lệ</t>
+  </si>
+  <si>
+    <t>Kiểm tra vé một chiều Economy, đặt trước dưới 7 ngày</t>
+  </si>
+  <si>
+    <t>Nhánh hợp lệ; đặt vé dưới 7 ngày</t>
+  </si>
+  <si>
+    <t>Kiểm tra khứ hồi, cuối tuần, hành lý 16kg, Silver</t>
+  </si>
+  <si>
+    <t>Nhánh khứ hồi; cuối tuần; phí hành lý Silver</t>
+  </si>
+  <si>
+    <t>Kiểm tra hạng Business</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Business", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh Business = True</t>
+  </si>
+  <si>
+    <t>Kiểm tra hạng FirstClass</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "FirstClass", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh FirstClass = True</t>
+  </si>
+  <si>
+    <t>Kiểm tra đặt trước từ 30 ngày</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 30, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh soNgayDatTruoc &gt;= 30</t>
+  </si>
+  <si>
+    <t>Kiểm tra đặt trước 7–29 ngày</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 7, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh soNgayDatTruoc &gt;= 7 &amp;&amp; &lt; 30</t>
+  </si>
+  <si>
+    <t>Kiểm tra ngày lễ trùng thứ Sáu</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 5, hanhLy = 5, thanhVien = "Thuong", ngayLe = true, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh ngayLe &amp;&amp; cuối tuần</t>
+  </si>
+  <si>
+    <t>Kiểm tra ngày lễ vào ngày thường</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = true, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh else if (ngayLe)</t>
+  </si>
+  <si>
+    <t>Kiểm tra cuối tuần không có ngày lễ</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 7, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh else if (thuBay == 5 || 6 || 7)</t>
+  </si>
+  <si>
+    <t>Kiểm tra hành lý trên 20kg</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 21, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh hanhLy &gt; 20</t>
+  </si>
+  <si>
+    <t>Kiểm tra hành lý trên 7kg đến 20kg</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 8, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh else if (hanhLy &gt; 7)</t>
+  </si>
+  <si>
+    <t>Kiểm tra giảm phí hành lý Gold</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 8, thanhVien = "Gold", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh Gold hoặc Platinum</t>
+  </si>
+  <si>
+    <t>Kiểm tra giảm phí hành lý Platinum</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 8, thanhVien = "Platinum", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Nhánh Platinum</t>
+  </si>
+  <si>
+    <t>TC15_Condition</t>
+  </si>
+  <si>
+    <t>Loại vé null</t>
+  </si>
+  <si>
+    <t>loaiVe = null, hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 1</t>
+  </si>
+  <si>
+    <t>TC16_Condition</t>
+  </si>
+  <si>
+    <t>Loại vé ngoài danh sách</t>
+  </si>
+  <si>
+    <t>loaiVe = "VIP", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 1</t>
+  </si>
+  <si>
+    <t>TC17_Condition</t>
+  </si>
+  <si>
+    <t>Loại vé MotChieu hợp lệ</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 1</t>
+  </si>
+  <si>
+    <t>TC18_Condition</t>
+  </si>
+  <si>
+    <t>Loại vé KhuHoi hợp lệ</t>
+  </si>
+  <si>
+    <t>loaiVe = "KhuHoi", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 1</t>
+  </si>
+  <si>
+    <t>TC19_Condition</t>
+  </si>
+  <si>
+    <t>Hạng ghế null</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = null, soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 2</t>
+  </si>
+  <si>
+    <t>TC20_Condition</t>
+  </si>
+  <si>
+    <t>Hạng ghế Economy hợp lệ</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 2</t>
+  </si>
+  <si>
+    <t>TC21_Condition</t>
+  </si>
+  <si>
+    <t>Hạng ghế Business hợp lệ</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 2</t>
+  </si>
+  <si>
+    <t>TC22_Condition</t>
+  </si>
+  <si>
+    <t>Hạng ghế FirstClass hợp lệ</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 2</t>
+  </si>
+  <si>
+    <t>TC23_Condition</t>
+  </si>
+  <si>
+    <t>Hạng ghế ngoài danh sách</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "VIP", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 5 bảng quyết định số 2</t>
+  </si>
+  <si>
+    <t>TC24_Condition</t>
+  </si>
+  <si>
+    <t>Thành viên null</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = null, ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>TC25_Condition</t>
+  </si>
+  <si>
+    <t>Thành viên Thuong hợp lệ</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>TC26_Condition</t>
+  </si>
+  <si>
+    <t>Thành viên Silver hợp lệ</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Silver", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>TC27_Condition</t>
+  </si>
+  <si>
+    <t>Thành viên Gold hợp lệ</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Gold", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>TC28_Condition</t>
+  </si>
+  <si>
+    <t>Thành viên Platinum hợp lệ</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Platinum", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 5 bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>TC29_Condition</t>
+  </si>
+  <si>
+    <t>Thành viên ngoài danh sách</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Diamond", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 6 bảng quyết định số 3</t>
+  </si>
+  <si>
+    <t>TC30_Condition</t>
+  </si>
+  <si>
+    <t>Số ngày đặt trước âm</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = -1, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC31_Condition</t>
+  </si>
+  <si>
+    <t>Thứ bay nhỏ hơn 1</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 0, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC32_Condition</t>
+  </si>
+  <si>
+    <t>Thứ bay lớn hơn 7</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 8, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC33_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý NaN</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = Double.NaN, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC34_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý âm</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = -1, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 5 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC35_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý trên 30kg</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 31, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 6 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC36_Condition</t>
+  </si>
+  <si>
+    <t>Giá vé không hữu hạn</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = Double.POSITIVE_INFINITY</t>
+  </si>
+  <si>
+    <t>Cột số 7 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC37_Condition</t>
+  </si>
+  <si>
+    <t>Giá vé cơ bản bằng 0</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 0</t>
+  </si>
+  <si>
+    <t>Cột số 8 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC38_Condition</t>
+  </si>
+  <si>
+    <t>Toàn bộ dữ liệu đầu vào hợp lệ</t>
+  </si>
+  <si>
+    <t>Cột số 9 bảng quyết định số 4</t>
+  </si>
+  <si>
+    <t>TC39_Condition</t>
+  </si>
+  <si>
+    <t>Không có ngày lễ (AND false)</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 5</t>
+  </si>
+  <si>
+    <t>TC40_Condition</t>
+  </si>
+  <si>
+    <t>Ngày lễ vào thứ Sáu</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 5</t>
+  </si>
+  <si>
+    <t>TC41_Condition</t>
+  </si>
+  <si>
+    <t>Ngày lễ vào thứ Bảy</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 6, hanhLy = 5, thanhVien = "Thuong", ngayLe = true, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 5</t>
+  </si>
+  <si>
+    <t>TC42_Condition</t>
+  </si>
+  <si>
+    <t>Ngày lễ vào Chủ nhật</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 7, hanhLy = 5, thanhVien = "Thuong", ngayLe = true, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 5</t>
+  </si>
+  <si>
+    <t>TC43_Condition</t>
+  </si>
+  <si>
+    <t>Ngày lễ không trùng cuối tuần</t>
+  </si>
+  <si>
+    <t>Cột số 5 bảng quyết định số 5</t>
+  </si>
+  <si>
+    <t>TC44_Condition</t>
+  </si>
+  <si>
+    <t>Điều kiện cuối tuần: thứ Sáu</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 5, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 6</t>
+  </si>
+  <si>
+    <t>TC45_Condition</t>
+  </si>
+  <si>
+    <t>Điều kiện cuối tuần: thứ Bảy</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 6, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 6</t>
+  </si>
+  <si>
+    <t>TC46_Condition</t>
+  </si>
+  <si>
+    <t>Điều kiện cuối tuần: Chủ nhật</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 6</t>
+  </si>
+  <si>
+    <t>TC47_Condition</t>
+  </si>
+  <si>
+    <t>Điều kiện cuối tuần: ngày thường</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 6</t>
+  </si>
+  <si>
+    <t>TC48_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &lt;= 7kg, không giảm phí</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 7</t>
+  </si>
+  <si>
+    <t>TC49_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &gt; 7kg, Gold giảm 20%</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 7</t>
+  </si>
+  <si>
+    <t>TC50_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &gt; 7kg, Platinum giảm 20%</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 7</t>
+  </si>
+  <si>
+    <t>TC51_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &gt; 7kg, không phải Gold/Platinum</t>
+  </si>
+  <si>
+    <t>Cột số 4 bảng quyết định số 7</t>
+  </si>
+  <si>
+    <t>TC52_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &lt;= 7kg, không áp dụng Silver</t>
+  </si>
+  <si>
+    <t>Cột số 1 bảng quyết định số 8</t>
+  </si>
+  <si>
+    <t>TC53_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &gt; 7kg, không phải Silver</t>
+  </si>
+  <si>
+    <t>Cột số 2 bảng quyết định số 8</t>
+  </si>
+  <si>
+    <t>TC54_Condition</t>
+  </si>
+  <si>
+    <t>Hành lý &gt; 7kg, Silver giảm 10%</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 8, thanhVien = "Silver", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>Cột số 3 bảng quyết định số 8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,8 +867,34 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -146,8 +907,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -170,17 +937,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -204,15 +1009,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>120650</xdr:colOff>
+      <xdr:colOff>340643</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>6622</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>482600</xdr:colOff>
-      <xdr:row>141</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>92658</xdr:colOff>
+      <xdr:row>133</xdr:row>
+      <xdr:rowOff>186693</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -241,8 +1046,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7156450" y="95250"/>
-          <a:ext cx="8286750" cy="25869900"/>
+          <a:off x="16775937" y="6622"/>
+          <a:ext cx="8328250" cy="26222542"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -552,29 +1357,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5076F25-3428-4630-81E5-51FDFE00A4B0}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="15.1796875" customWidth="1"/>
     <col min="3" max="3" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="33.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -591,7 +1396,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -608,7 +1413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>2</v>
       </c>
@@ -636,105 +1441,1801 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F7F2656-C2F3-45D0-B2D5-24D480F4A636}">
-  <dimension ref="A1:Y10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:CA56"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.54296875" customWidth="1"/>
-    <col min="2" max="2" width="12.36328125" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" customWidth="1"/>
-    <col min="4" max="4" width="17.08984375" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="178.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.453125" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="65.54296875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="101.90625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="128.81640625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="121.26953125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="47.90625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="65.54296875" bestFit="1" customWidth="1"/>
+    <col min="76" max="76" width="36.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+    <row r="1" spans="1:79" ht="16.5">
+      <c r="A1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="AE1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT1" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE1" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="BL1" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="BR1" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="BX1" s="9" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:79" ht="16.5">
+      <c r="A2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="13" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="Y2" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL2" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AT2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="AU2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AV2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AW2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AX2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE2" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BG2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BM2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BO2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BP2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="BS2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BT2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BU2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BV2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BX2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="BY2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BZ2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="CA2" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:79" ht="16.5">
+      <c r="A3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
+      <c r="B3" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="D3" s="12" t="s">
         <v>24</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="AF3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AP3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AU3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AW3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AX3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="BF3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BI3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BM3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BO3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BP3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BT3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BU3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BV3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BX3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BY3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BZ3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="CA3" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:79" ht="16.5">
+      <c r="A4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1200000</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AF4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="AM4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="AU4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="BF4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BH4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BJ4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BM4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BO4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BP4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="BS4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BT4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BU4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BV4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BX4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="BY4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BZ4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="CA4" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:79" ht="16.5">
+      <c r="A5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2748600</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y5" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AC5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AE5" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AI5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AR5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT5" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="AU5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AZ5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE5" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="BF5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BG5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BH5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BI5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="BM5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BN5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BO5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BP5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BR5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="BS5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BT5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BU5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BV5" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" spans="1:79" ht="16.5">
+      <c r="A6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="12">
+        <v>1900000</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="AM6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AN6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AO6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AP6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AQ6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT6" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AU6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BA6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BE6" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BG6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BH6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ6" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:79" ht="16.5">
+      <c r="A7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="12">
+        <v>2850000</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AP7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="AU7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AZ7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BA7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BB7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC7" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:79" ht="16.5">
+      <c r="A8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D8" s="12">
+        <v>850000</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="AT8" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AU8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AZ8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA8" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB8" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="BC8" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:79" ht="16.5">
+      <c r="A9" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="AT9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AU9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AW9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AX9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AZ9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BA9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="BB9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BC9" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:79" ht="12.5" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1282500</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="AT10" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AU10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AV10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AW10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AX10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AY10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AZ10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BA10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BB10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BC10" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:79" ht="16.5">
+      <c r="A11" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1187500</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" spans="1:79" ht="16.5">
+      <c r="A12" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1045000</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:79" ht="16.5">
+      <c r="A13" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D13" s="12">
+        <v>1250000</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="14" spans="1:79" ht="16.5">
+      <c r="A14" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="12">
+        <v>1100000</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:79" ht="16.5">
+      <c r="A15" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="12">
+        <v>1070000</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:79" ht="16.5">
+      <c r="A16" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1070000</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" ht="16.5">
+      <c r="A17" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" ht="16.5">
+      <c r="A18" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="16.5">
+      <c r="A19" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D19" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" ht="16.5">
+      <c r="A20" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="12">
+        <v>1710000</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="16.5">
+      <c r="A21" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" ht="16.5">
+      <c r="A22" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="Y22" s="4"/>
+    </row>
+    <row r="23" spans="1:25" ht="16.5">
+      <c r="A23" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="12">
+        <v>1900000</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" ht="16.5">
+      <c r="A24" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="12">
+        <v>2850000</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" ht="16.5">
+      <c r="A25" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" ht="16.5">
+      <c r="A26" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D26" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" ht="16.5">
+      <c r="A27" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" ht="16.5">
+      <c r="A28" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" ht="16.5">
+      <c r="A29" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" ht="16.5">
+      <c r="A30" s="11" t="s">
+        <v>176</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="D30" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="16.5">
+      <c r="A31" s="11" t="s">
+        <v>180</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="16.5">
+      <c r="A32" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16.5">
+      <c r="A33" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16.5">
+      <c r="A34" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16.5">
+      <c r="A35" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16.5">
+      <c r="A36" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16.5">
+      <c r="A37" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16.5">
+      <c r="A38" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16.5">
+      <c r="A39" s="11" t="s">
+        <v>212</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>214</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16.5">
+      <c r="A40" s="11" t="s">
+        <v>216</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16.5">
+      <c r="A41" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16.5">
+      <c r="A42" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="12">
+        <v>1282500</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16.5">
+      <c r="A43" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="D43" s="12">
+        <v>1282500</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16.5">
+      <c r="A44" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D44" s="12">
+        <v>1282500</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16.5">
+      <c r="A45" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D45" s="12">
+        <v>1187500</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16.5">
+      <c r="A46" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="D46" s="12">
+        <v>1045000</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16.5">
+      <c r="A47" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="D47" s="12">
+        <v>1045000</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16.5">
+      <c r="A48" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="D48" s="12">
+        <v>1045000</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.5">
+      <c r="A49" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D49" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16.5">
+      <c r="A50" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="D50" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="16.5">
+      <c r="A51" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="D51" s="12">
+        <v>1070000</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16.5">
+      <c r="A52" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="D52" s="12">
+        <v>1070000</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="16.5">
+      <c r="A53" s="11" t="s">
+        <v>259</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D53" s="12">
+        <v>1100000</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="16.5">
+      <c r="A54" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="D54" s="12">
+        <v>950000</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="16.5">
+      <c r="A55" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="D55" s="12">
+        <v>1100000</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16.5">
+      <c r="A56" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D56" s="12">
+        <v>1085000</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D49E8C-3D16-4DF4-BEED-63520DF02D1C}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/09_02.xlsx
+++ b/09_02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DuLieuCua_Sang\HK261\Testing\Project\09_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3858C1D5-D35D-4471-AE48-63002F3A58B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CBDD27-AAB0-4561-88B4-A2FA18A8A4C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{24A087C9-FC7B-41A3-BD57-B9096DC3F569}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="271">
   <si>
     <t>ĐỒ ÁN CUỐI KÌ</t>
   </si>
@@ -95,9 +95,6 @@
     <t>Chuoj hình kết quả các testcases Failed</t>
   </si>
   <si>
-    <t>Xuất toàn bộ kết quả ra file JUnitTestResult.csv</t>
-  </si>
-  <si>
     <t>loaiVe = "MotChieu", hangGhe = "Business", soNgayDatTruoc = -4, thuBay = 4, hanhLy = 5, thanhVien = "Silver", ngayLe = true, giaVeCoBan = 1200000</t>
   </si>
   <si>
@@ -623,9 +620,6 @@
     <t>Hành lý NaN</t>
   </si>
   <si>
-    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = Double.NaN, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
-  </si>
-  <si>
     <t>Cột số 4 bảng quyết định số 4</t>
   </si>
   <si>
@@ -659,9 +653,6 @@
     <t>Giá vé không hữu hạn</t>
   </si>
   <si>
-    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = Double.POSITIVE_INFINITY</t>
-  </si>
-  <si>
     <t>Cột số 7 bảng quyết định số 4</t>
   </si>
   <si>
@@ -843,6 +834,12 @@
   </si>
   <si>
     <t>Cột số 3 bảng quyết định số 8</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = NaN, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = 1000000</t>
+  </si>
+  <si>
+    <t>loaiVe = "MotChieu", hangGhe = "Economy", soNgayDatTruoc = 15, thuBay = 2, hanhLy = 5, thanhVien = "Thuong", ngayLe = false, giaVeCoBan = INFINITY</t>
   </si>
 </sst>
 </file>
@@ -1016,8 +1013,8 @@
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>92658</xdr:colOff>
-      <xdr:row>133</xdr:row>
-      <xdr:rowOff>186693</xdr:rowOff>
+      <xdr:row>134</xdr:row>
+      <xdr:rowOff>1965</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1048,6 +1045,55 @@
         <a:xfrm>
           <a:off x="16775937" y="6622"/>
           <a:ext cx="8328250" cy="26222542"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>591050</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>159137</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65598BC6-34C0-73C9-233C-AD2AD547D230}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="9735050" cy="7525137"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1448,7 +1494,7 @@
     <col min="2" max="2" width="46.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="178.1796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.7265625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="65.54296875" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="101.90625" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="128.81640625" bestFit="1" customWidth="1"/>
@@ -1464,28 +1510,28 @@
         <v>20</v>
       </c>
       <c r="Y1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="AE1" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AL1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="AL1" s="6" t="s">
+      <c r="AT1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="AT1" s="6" t="s">
+      <c r="BE1" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="BE1" s="9" t="s">
+      <c r="BL1" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="BL1" s="9" t="s">
-        <v>77</v>
-      </c>
       <c r="BR1" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="BX1" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:79" ht="16.5">
@@ -1505,148 +1551,148 @@
         <v>18</v>
       </c>
       <c r="Y2" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE2" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Z2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE2" s="5" t="s">
+      <c r="AF2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="AG2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AL2" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="AF2" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AH2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="AM2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AN2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AO2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AP2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AR2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AT2" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AU2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AV2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AW2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AX2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AY2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AZ2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BA2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BB2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BE2" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="BF2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BG2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BH2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BI2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BJ2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BL2" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BM2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BN2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BO2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BP2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BR2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="BS2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BT2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BU2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BV2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BX2" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="BY2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BZ2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="CA2" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:79" ht="16.5">
@@ -1654,1566 +1700,1566 @@
         <v>19</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>90</v>
-      </c>
       <c r="Y3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Z3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AC3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AE3" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AF3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AG3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AI3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AL3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AM3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AN3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AO3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AP3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AR3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AT3" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AU3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AW3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AX3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AY3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AZ3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BA3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BB3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BE3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BG3" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="BH3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BI3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ3" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BL3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="BF3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="BG3" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="BH3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BI3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BJ3" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BL3" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="BM3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BN3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BO3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BP3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BR3" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="BS3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BT3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BU3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BV3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BX3" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="BY3" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BZ3" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="CA3" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:79" ht="16.5">
       <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="D4" s="12">
         <v>1200000</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y4" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AA4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AC4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AE4" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AF4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AG4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AI4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AJ4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AL4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AM4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AN4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AP4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AQ4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AR4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AT4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AU4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AW4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AX4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AY4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AZ4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BA4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BB4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BE4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="BF4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BG4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BH4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="BI4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BJ4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BL4" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="BF4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="BG4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="BH4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="BI4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BJ4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BL4" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="BM4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BN4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BO4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BP4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BR4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="BS4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BT4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="BU4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="BV4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="BX4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="BS4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="BT4" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="BU4" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="BV4" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="BX4" s="1" t="s">
-        <v>85</v>
-      </c>
       <c r="BY4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BZ4" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="CA4" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:79" ht="16.5">
       <c r="A5" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5" s="12">
         <v>2748600</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AA5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AB5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AC5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AE5" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AF5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AG5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AH5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AI5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AJ5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AL5" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AM5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AN5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AP5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AR5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AT5" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AU5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AW5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AX5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AY5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AZ5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BA5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BB5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BE5" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="BF5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BG5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BH5" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BI5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BJ5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BL5" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BM5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BN5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BO5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BP5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BR5" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BS5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BT5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BU5" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BV5" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:79" ht="16.5">
       <c r="A6" s="11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="D6" s="12">
+        <v>2900000</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="12">
-        <v>1900000</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>97</v>
-      </c>
       <c r="AE6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AF6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AG6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AH6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AI6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AJ6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AL6" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AM6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AN6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AO6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AP6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AQ6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AR6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AT6" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AU6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AW6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AX6" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AZ6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BA6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BB6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BE6" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="BF6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BG6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BH6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BI6" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BJ6" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:79" ht="16.5">
       <c r="A7" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="11" t="s">
         <v>98</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>99</v>
       </c>
       <c r="D7" s="12">
         <v>2850000</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AL7" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AM7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AN7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AO7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AP7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AQ7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AR7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AT7" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AU7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AW7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AX7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY7" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AZ7" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BA7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BB7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC7" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:79" ht="16.5">
       <c r="A8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="D8" s="12">
         <v>850000</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AT8" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="AU8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AW8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AX8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AZ8" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BA8" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BB8" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="BC8" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:79" ht="16.5">
       <c r="A9" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>105</v>
       </c>
       <c r="D9" s="12">
         <v>950000</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AT9" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AU9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AV9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AW9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AX9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AY9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="AZ9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BA9" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="BB9" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BC9" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:79" ht="12.5" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="D10" s="12">
         <v>1282500</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AT10" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AU10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AV10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AW10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AX10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AY10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="AZ10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BA10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BB10" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="BC10" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:79" ht="16.5">
       <c r="A11" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="D11" s="12">
         <v>1187500</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:79" ht="16.5">
       <c r="A12" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="D12" s="12">
         <v>1045000</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:79" ht="16.5">
       <c r="A13" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>117</v>
       </c>
       <c r="D13" s="12">
         <v>1250000</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:79" ht="16.5">
       <c r="A14" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>120</v>
       </c>
       <c r="D14" s="12">
         <v>1100000</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:79" ht="16.5">
       <c r="A15" s="11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="D15" s="12">
         <v>1070000</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:79" ht="16.5">
       <c r="A16" s="11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>125</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>126</v>
       </c>
       <c r="D16" s="12">
         <v>1070000</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:25" ht="16.5">
       <c r="A17" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="D17" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>130</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:25" ht="16.5">
       <c r="A18" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B18" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="D18" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:25" ht="16.5">
       <c r="A19" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>137</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>138</v>
       </c>
       <c r="D19" s="12">
         <v>950000</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:25" ht="16.5">
       <c r="A20" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="D20" s="12">
         <v>1710000</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="21" spans="1:25" ht="16.5">
       <c r="A21" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="D21" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E21" s="11" t="s">
         <v>146</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:25" ht="16.5">
       <c r="A22" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>149</v>
-      </c>
       <c r="C22" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D22" s="12">
         <v>950000</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Y22" s="4"/>
     </row>
     <row r="23" spans="1:25" ht="16.5">
       <c r="A23" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="11" t="s">
-        <v>152</v>
-      </c>
       <c r="C23" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D23" s="12">
         <v>1900000</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:25" ht="16.5">
       <c r="A24" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>155</v>
-      </c>
       <c r="C24" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D24" s="12">
         <v>2850000</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:25" ht="16.5">
       <c r="A25" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="C25" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="D25" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>159</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:25" ht="16.5">
       <c r="A26" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="C26" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="D26" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E26" s="11" t="s">
         <v>163</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:25" ht="16.5">
       <c r="A27" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="C27" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D27" s="12">
+        <v>940000</v>
+      </c>
+      <c r="E27" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D27" s="12">
-        <v>950000</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:25" ht="16.5">
       <c r="A28" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="B28" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="C28" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="D28" s="12">
+        <v>940000</v>
+      </c>
+      <c r="E28" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="D28" s="12">
-        <v>950000</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:25" ht="16.5">
       <c r="A29" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="C29" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="12">
+        <v>940000</v>
+      </c>
+      <c r="E29" s="11" t="s">
         <v>174</v>
-      </c>
-      <c r="D29" s="12">
-        <v>950000</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:25" ht="16.5">
       <c r="A30" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="D30" s="12">
         <v>950000</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31" spans="1:25" ht="16.5">
       <c r="A31" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="C31" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="D31" s="12">
+        <v>1000000</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>182</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:25" ht="16.5">
       <c r="A32" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B32" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="C32" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="D32" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>186</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.5">
       <c r="A33" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="C33" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="D33" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5">
       <c r="A34" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="C34" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="D34" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>194</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5">
       <c r="A35" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="B35" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="C35" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>197</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="11" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="16.5">
       <c r="A36" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>200</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="D36" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>201</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.5">
       <c r="A37" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="D37" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>205</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="D37" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5">
       <c r="A38" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>208</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.5">
       <c r="A39" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>211</v>
+      </c>
+      <c r="D39" s="12">
+        <v>-1</v>
+      </c>
+      <c r="E39" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16.5">
       <c r="A40" s="11" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D40" s="12">
         <v>950000</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5">
       <c r="A41" s="11" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41" s="12">
         <v>950000</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5">
       <c r="A42" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D42" s="12">
-        <v>1282500</v>
+        <v>1202500</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="16.5">
       <c r="A43" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="D43" s="12">
+        <v>1202500</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>225</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="D43" s="12">
-        <v>1282500</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="16.5">
       <c r="A44" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D44" s="12">
+        <v>1202500</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>229</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>230</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D44" s="12">
-        <v>1282500</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5">
       <c r="A45" s="11" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D45" s="12">
         <v>1187500</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5">
       <c r="A46" s="11" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D46" s="12">
         <v>1045000</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="16.5">
       <c r="A47" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" s="12">
+        <v>1044000</v>
+      </c>
+      <c r="E47" s="11" t="s">
         <v>240</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="D47" s="12">
-        <v>1045000</v>
-      </c>
-      <c r="E47" s="11" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="16.5">
       <c r="A48" s="11" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D48" s="12">
-        <v>1045000</v>
+        <v>1044000</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="16.5">
       <c r="A49" s="11" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D49" s="12">
         <v>950000</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5">
       <c r="A50" s="11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D50" s="12">
         <v>950000</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5">
       <c r="A51" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D51" s="12">
         <v>1070000</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="16.5">
       <c r="A52" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D52" s="12">
         <v>1070000</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5">
       <c r="A53" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D53" s="12">
         <v>1100000</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5">
       <c r="A54" s="11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D54" s="12">
         <v>950000</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.5">
       <c r="A55" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D55" s="12">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5">
       <c r="A56" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D56" s="12">
         <v>1085000</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3271,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D49E8C-3D16-4DF4-BEED-63520DF02D1C}">
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3233,12 +3279,8 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>